--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10160,10 +10160,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119998328</v>
+        <v>119998685</v>
       </c>
       <c r="B78" t="n">
-        <v>97907</v>
+        <v>91861</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10172,25 +10172,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -10200,15 +10200,10 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -10216,13 +10211,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>558599</v>
+        <v>558654</v>
       </c>
       <c r="R78" t="n">
-        <v>6836259</v>
+        <v>6836334</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10279,10 +10274,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119998685</v>
+        <v>119996727</v>
       </c>
       <c r="B79" t="n">
-        <v>91861</v>
+        <v>78526</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10291,25 +10286,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -10319,7 +10314,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -10330,10 +10325,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>558654</v>
+        <v>558730</v>
       </c>
       <c r="R79" t="n">
-        <v>6836334</v>
+        <v>6836360</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10393,10 +10388,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119996727</v>
+        <v>119998328</v>
       </c>
       <c r="B80" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10405,25 +10400,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -10433,10 +10428,15 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10444,13 +10444,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>558730</v>
+        <v>558599</v>
       </c>
       <c r="R80" t="n">
-        <v>6836360</v>
+        <v>6836259</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10274,10 +10274,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119996727</v>
+        <v>119998328</v>
       </c>
       <c r="B79" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10286,25 +10286,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -10314,10 +10314,15 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -10325,13 +10330,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>558730</v>
+        <v>558599</v>
       </c>
       <c r="R79" t="n">
-        <v>6836360</v>
+        <v>6836259</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10388,10 +10393,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119998328</v>
+        <v>119996727</v>
       </c>
       <c r="B80" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10400,25 +10405,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -10428,15 +10433,10 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10444,13 +10444,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>558599</v>
+        <v>558730</v>
       </c>
       <c r="R80" t="n">
-        <v>6836259</v>
+        <v>6836360</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10160,10 +10160,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119998685</v>
+        <v>119998328</v>
       </c>
       <c r="B78" t="n">
-        <v>91861</v>
+        <v>97907</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10172,25 +10172,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -10200,10 +10200,15 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -10211,13 +10216,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>558654</v>
+        <v>558599</v>
       </c>
       <c r="R78" t="n">
-        <v>6836334</v>
+        <v>6836259</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10274,10 +10279,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119998328</v>
+        <v>119996727</v>
       </c>
       <c r="B79" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10286,25 +10291,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -10314,15 +10319,10 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -10330,13 +10330,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>558599</v>
+        <v>558730</v>
       </c>
       <c r="R79" t="n">
-        <v>6836259</v>
+        <v>6836360</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10393,10 +10393,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119996727</v>
+        <v>119998685</v>
       </c>
       <c r="B80" t="n">
-        <v>78526</v>
+        <v>91861</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10405,25 +10405,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -10444,10 +10444,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>558730</v>
+        <v>558654</v>
       </c>
       <c r="R80" t="n">
-        <v>6836360</v>
+        <v>6836334</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10160,10 +10160,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119998328</v>
+        <v>119998685</v>
       </c>
       <c r="B78" t="n">
-        <v>97907</v>
+        <v>91879</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10172,25 +10172,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -10200,15 +10200,10 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -10216,13 +10211,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>558599</v>
+        <v>558654</v>
       </c>
       <c r="R78" t="n">
-        <v>6836259</v>
+        <v>6836334</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10282,7 +10277,7 @@
         <v>119996727</v>
       </c>
       <c r="B79" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10393,10 +10388,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119998685</v>
+        <v>119998328</v>
       </c>
       <c r="B80" t="n">
-        <v>91861</v>
+        <v>97930</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10405,25 +10400,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -10433,10 +10428,15 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10444,13 +10444,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>558654</v>
+        <v>558599</v>
       </c>
       <c r="R80" t="n">
-        <v>6836334</v>
+        <v>6836259</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10274,10 +10274,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119996727</v>
+        <v>119998328</v>
       </c>
       <c r="B79" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10286,25 +10286,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -10314,10 +10314,15 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -10325,13 +10330,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>558730</v>
+        <v>558599</v>
       </c>
       <c r="R79" t="n">
-        <v>6836360</v>
+        <v>6836259</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10388,10 +10393,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119998328</v>
+        <v>119996727</v>
       </c>
       <c r="B80" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10400,25 +10405,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -10428,15 +10433,10 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10444,13 +10444,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>558599</v>
+        <v>558730</v>
       </c>
       <c r="R80" t="n">
-        <v>6836259</v>
+        <v>6836360</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10274,10 +10274,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119998328</v>
+        <v>119996727</v>
       </c>
       <c r="B79" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10286,25 +10286,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -10314,15 +10314,10 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -10330,13 +10325,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>558599</v>
+        <v>558730</v>
       </c>
       <c r="R79" t="n">
-        <v>6836259</v>
+        <v>6836360</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10393,10 +10388,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119996727</v>
+        <v>119998328</v>
       </c>
       <c r="B80" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10405,25 +10400,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -10433,10 +10428,15 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10444,13 +10444,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>558730</v>
+        <v>558599</v>
       </c>
       <c r="R80" t="n">
-        <v>6836360</v>
+        <v>6836259</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10160,10 +10160,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119998685</v>
+        <v>119996727</v>
       </c>
       <c r="B78" t="n">
-        <v>91879</v>
+        <v>78542</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10172,25 +10172,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -10211,10 +10211,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>558654</v>
+        <v>558730</v>
       </c>
       <c r="R78" t="n">
-        <v>6836334</v>
+        <v>6836360</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10274,10 +10274,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119996727</v>
+        <v>119998328</v>
       </c>
       <c r="B79" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10286,25 +10286,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -10314,10 +10314,15 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -10325,13 +10330,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>558730</v>
+        <v>558599</v>
       </c>
       <c r="R79" t="n">
-        <v>6836360</v>
+        <v>6836259</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10388,10 +10393,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119998328</v>
+        <v>119998685</v>
       </c>
       <c r="B80" t="n">
-        <v>97930</v>
+        <v>91879</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10400,25 +10405,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -10428,15 +10433,10 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10444,13 +10444,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>558599</v>
+        <v>558654</v>
       </c>
       <c r="R80" t="n">
-        <v>6836259</v>
+        <v>6836334</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10274,10 +10274,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119998328</v>
+        <v>119998685</v>
       </c>
       <c r="B79" t="n">
-        <v>97930</v>
+        <v>91879</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10286,25 +10286,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -10314,15 +10314,10 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -10330,13 +10325,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>558599</v>
+        <v>558654</v>
       </c>
       <c r="R79" t="n">
-        <v>6836259</v>
+        <v>6836334</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10393,10 +10388,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119998685</v>
+        <v>119998328</v>
       </c>
       <c r="B80" t="n">
-        <v>91879</v>
+        <v>97930</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10405,25 +10400,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -10433,10 +10428,15 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10444,13 +10444,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>558654</v>
+        <v>558599</v>
       </c>
       <c r="R80" t="n">
-        <v>6836334</v>
+        <v>6836259</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10274,10 +10274,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119998685</v>
+        <v>119998328</v>
       </c>
       <c r="B79" t="n">
-        <v>91879</v>
+        <v>97930</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10286,25 +10286,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -10314,10 +10314,15 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -10325,13 +10330,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>558654</v>
+        <v>558599</v>
       </c>
       <c r="R79" t="n">
-        <v>6836334</v>
+        <v>6836259</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10388,10 +10393,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119998328</v>
+        <v>119998685</v>
       </c>
       <c r="B80" t="n">
-        <v>97930</v>
+        <v>91879</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10400,25 +10405,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -10428,15 +10433,10 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10444,13 +10444,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>558599</v>
+        <v>558654</v>
       </c>
       <c r="R80" t="n">
-        <v>6836259</v>
+        <v>6836334</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>88047131</v>
       </c>
       <c r="B2" t="n">
-        <v>89406</v>
+        <v>90971</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558658.7425014997</v>
+        <v>558659</v>
       </c>
       <c r="R2" t="n">
-        <v>6836342.80301825</v>
+        <v>6836343</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +751,9 @@
           <t>2020-09-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +779,7 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -804,7 +794,7 @@
         <v>88042293</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
+        <v>90957</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -844,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558647.2009530754</v>
+        <v>558647</v>
       </c>
       <c r="R3" t="n">
-        <v>6836405.804862944</v>
+        <v>6836406</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,19 +867,9 @@
           <t>2020-09-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +895,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -930,7 +910,7 @@
         <v>88047210</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
+        <v>90957</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -970,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558667.6630799621</v>
+        <v>558668</v>
       </c>
       <c r="R4" t="n">
-        <v>6836294.011043417</v>
+        <v>6836294</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,19 +983,9 @@
           <t>2020-09-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,12 +1011,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1056,7 +1026,7 @@
         <v>88046405</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1097,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558847.9666180873</v>
+        <v>558848</v>
       </c>
       <c r="R5" t="n">
-        <v>6836520.889285344</v>
+        <v>6836521</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,19 +1100,9 @@
           <t>2020-09-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,7 +1128,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1183,7 +1143,7 @@
         <v>88046755</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
+        <v>90957</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1223,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558605.1851311801</v>
+        <v>558605</v>
       </c>
       <c r="R6" t="n">
-        <v>6836245.904789639</v>
+        <v>6836246</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,19 +1216,9 @@
           <t>2020-09-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-09-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,7 +1244,7 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -1309,7 +1259,7 @@
         <v>88042353</v>
       </c>
       <c r="B7" t="n">
-        <v>56411</v>
+        <v>57497</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1358,10 +1308,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558667.9020753475</v>
+        <v>558668</v>
       </c>
       <c r="R7" t="n">
-        <v>6836363.866677043</v>
+        <v>6836364</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1391,19 +1341,9 @@
           <t>2020-09-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-09-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1433,7 +1373,7 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -1448,7 +1388,7 @@
         <v>88048734</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1489,10 +1429,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558682.6305446294</v>
+        <v>558683</v>
       </c>
       <c r="R8" t="n">
-        <v>6836449.172796553</v>
+        <v>6836449</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1522,19 +1462,9 @@
           <t>2020-09-05</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-09-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1560,7 +1490,7 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1575,7 +1505,7 @@
         <v>88046342</v>
       </c>
       <c r="B9" t="n">
-        <v>56411</v>
+        <v>57497</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1624,10 +1554,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558919.8128566303</v>
+        <v>558920</v>
       </c>
       <c r="R9" t="n">
-        <v>6836438.012907561</v>
+        <v>6836438</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1657,19 +1587,9 @@
           <t>2020-09-05</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-09-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1699,7 +1619,7 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -1714,7 +1634,7 @@
         <v>88042206</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1755,10 +1675,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558646.1605564525</v>
+        <v>558646</v>
       </c>
       <c r="R10" t="n">
-        <v>6836411.014031377</v>
+        <v>6836411</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1788,19 +1708,9 @@
           <t>2020-09-05</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-09-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1826,7 +1736,7 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -1841,7 +1751,7 @@
         <v>88047659</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1882,10 +1792,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558652.9637522637</v>
+        <v>558653</v>
       </c>
       <c r="R11" t="n">
-        <v>6836262.873750673</v>
+        <v>6836263</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1915,19 +1825,9 @@
           <t>2020-09-05</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-09-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1953,12 +1853,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1968,7 +1868,7 @@
         <v>88047287</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2009,10 +1909,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558723.1937867266</v>
+        <v>558723</v>
       </c>
       <c r="R12" t="n">
-        <v>6836386.666048735</v>
+        <v>6836387</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2042,19 +1942,9 @@
           <t>2020-09-05</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-09-05</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2080,12 +1970,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2095,7 +1985,7 @@
         <v>88046669</v>
       </c>
       <c r="B13" t="n">
-        <v>89392</v>
+        <v>90957</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2135,10 +2025,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558645.8423208453</v>
+        <v>558646</v>
       </c>
       <c r="R13" t="n">
-        <v>6836289.838315063</v>
+        <v>6836290</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2168,19 +2058,9 @@
           <t>2020-09-05</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2020-09-05</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2206,7 +2086,7 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -2221,7 +2101,7 @@
         <v>88046386</v>
       </c>
       <c r="B14" t="n">
-        <v>89392</v>
+        <v>90957</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2261,10 +2141,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558917.2116939216</v>
+        <v>558917</v>
       </c>
       <c r="R14" t="n">
-        <v>6836478.832582386</v>
+        <v>6836479</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2294,19 +2174,9 @@
           <t>2020-09-05</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2020-09-05</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2332,7 +2202,7 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -2347,7 +2217,7 @@
         <v>88046784</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2388,10 +2258,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558576.0671415837</v>
+        <v>558576</v>
       </c>
       <c r="R15" t="n">
-        <v>6836167.002445312</v>
+        <v>6836167</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2421,19 +2291,9 @@
           <t>2020-09-05</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2020-09-05</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2459,7 +2319,7 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -2474,7 +2334,7 @@
         <v>88046296</v>
       </c>
       <c r="B16" t="n">
-        <v>89673</v>
+        <v>91244</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2514,10 +2374,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558665.8927846086</v>
+        <v>558666</v>
       </c>
       <c r="R16" t="n">
-        <v>6836398.044983066</v>
+        <v>6836398</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2547,19 +2407,9 @@
           <t>2020-09-05</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2020-09-05</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2585,7 +2435,7 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -2600,7 +2450,7 @@
         <v>88558798</v>
       </c>
       <c r="B17" t="n">
-        <v>93044</v>
+        <v>94771</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2641,10 +2491,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558691.128085145</v>
+        <v>558691</v>
       </c>
       <c r="R17" t="n">
-        <v>6836313.417785704</v>
+        <v>6836313</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2674,19 +2524,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2702,7 +2542,7 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -2717,7 +2557,7 @@
         <v>88559378</v>
       </c>
       <c r="B18" t="n">
-        <v>93044</v>
+        <v>94771</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2758,10 +2598,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558686.5039001082</v>
+        <v>558687</v>
       </c>
       <c r="R18" t="n">
-        <v>6836389.367509373</v>
+        <v>6836389</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2791,19 +2631,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2819,12 +2649,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2834,7 +2664,7 @@
         <v>88559468</v>
       </c>
       <c r="B19" t="n">
-        <v>93044</v>
+        <v>94771</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2883,10 +2713,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558669.7808634135</v>
+        <v>558670</v>
       </c>
       <c r="R19" t="n">
-        <v>6836365.324176324</v>
+        <v>6836365</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2916,19 +2746,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2944,12 +2764,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2959,7 +2779,7 @@
         <v>88558994</v>
       </c>
       <c r="B20" t="n">
-        <v>93044</v>
+        <v>94771</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3000,10 +2820,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558655.0344480986</v>
+        <v>558655</v>
       </c>
       <c r="R20" t="n">
-        <v>6836309.002074209</v>
+        <v>6836309</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3033,19 +2853,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3061,7 +2871,7 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -3076,7 +2886,7 @@
         <v>88558895</v>
       </c>
       <c r="B21" t="n">
-        <v>93044</v>
+        <v>94771</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3117,10 +2927,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558595.1373149314</v>
+        <v>558595</v>
       </c>
       <c r="R21" t="n">
-        <v>6836249.060352077</v>
+        <v>6836249</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3150,19 +2960,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3178,7 +2978,7 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -3193,7 +2993,7 @@
         <v>88558775</v>
       </c>
       <c r="B22" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3234,10 +3034,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558703.9237956484</v>
+        <v>558704</v>
       </c>
       <c r="R22" t="n">
-        <v>6836344.52239414</v>
+        <v>6836345</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3267,19 +3067,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3295,7 +3085,7 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -3310,7 +3100,7 @@
         <v>88559291</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3355,10 +3145,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558686.5039001082</v>
+        <v>558687</v>
       </c>
       <c r="R23" t="n">
-        <v>6836389.367509373</v>
+        <v>6836389</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3388,19 +3178,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3416,12 +3196,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3431,7 +3211,7 @@
         <v>88559031</v>
       </c>
       <c r="B24" t="n">
-        <v>93044</v>
+        <v>94771</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3472,10 +3252,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558616.2915391909</v>
+        <v>558616</v>
       </c>
       <c r="R24" t="n">
-        <v>6836460.398471966</v>
+        <v>6836460</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3505,19 +3285,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3533,7 +3303,7 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -3548,7 +3318,7 @@
         <v>88559451</v>
       </c>
       <c r="B25" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3601,10 +3371,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558669.2913067308</v>
+        <v>558669</v>
       </c>
       <c r="R25" t="n">
-        <v>6836310.195020606</v>
+        <v>6836310</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3634,19 +3404,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3662,12 +3422,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3802,7 +3562,7 @@
         <v>91007790</v>
       </c>
       <c r="B27" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3843,10 +3603,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558677.1411256079</v>
+        <v>558677</v>
       </c>
       <c r="R27" t="n">
-        <v>6836408.21499195</v>
+        <v>6836408</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3876,19 +3636,9 @@
           <t>2020-10-03</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2020-10-03</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3904,12 +3654,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3919,7 +3669,7 @@
         <v>96247076</v>
       </c>
       <c r="B28" t="n">
-        <v>89588</v>
+        <v>91166</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3967,10 +3717,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558658.535996907</v>
+        <v>558659</v>
       </c>
       <c r="R28" t="n">
-        <v>6836466.818942238</v>
+        <v>6836467</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4000,19 +3750,9 @@
           <t>2021-09-15</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4033,12 +3773,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4048,7 +3788,7 @@
         <v>96247188</v>
       </c>
       <c r="B29" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4105,10 +3845,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558639.6031234931</v>
+        <v>558640</v>
       </c>
       <c r="R29" t="n">
-        <v>6836460.794908416</v>
+        <v>6836461</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4138,19 +3878,9 @@
           <t>2021-08-04</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4171,12 +3901,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4186,7 +3916,7 @@
         <v>96247391</v>
       </c>
       <c r="B30" t="n">
-        <v>93044</v>
+        <v>94771</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4235,10 +3965,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558662.2726499656</v>
+        <v>558662</v>
       </c>
       <c r="R30" t="n">
-        <v>6836387.054427391</v>
+        <v>6836387</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4268,19 +3998,9 @@
           <t>2021-08-29</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4296,12 +4016,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4311,7 +4031,7 @@
         <v>96247229</v>
       </c>
       <c r="B31" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4364,10 +4084,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558650.8038997207</v>
+        <v>558651</v>
       </c>
       <c r="R31" t="n">
-        <v>6836445.780211212</v>
+        <v>6836446</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4397,19 +4117,9 @@
           <t>2021-08-04</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4430,12 +4140,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4445,7 +4155,7 @@
         <v>96247334</v>
       </c>
       <c r="B32" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4502,10 +4212,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558679.3147629659</v>
+        <v>558679</v>
       </c>
       <c r="R32" t="n">
-        <v>6836308.464870641</v>
+        <v>6836308</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4535,19 +4245,9 @@
           <t>2021-08-04</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4568,12 +4268,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4583,7 +4283,7 @@
         <v>96247262</v>
       </c>
       <c r="B33" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4640,10 +4340,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558717.3002052831</v>
+        <v>558717</v>
       </c>
       <c r="R33" t="n">
-        <v>6836369.459394456</v>
+        <v>6836369</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4673,19 +4373,9 @@
           <t>2021-08-04</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4701,12 +4391,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4716,7 +4406,7 @@
         <v>96247366</v>
       </c>
       <c r="B34" t="n">
-        <v>93044</v>
+        <v>94771</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4765,10 +4455,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558673.5546037845</v>
+        <v>558674</v>
       </c>
       <c r="R34" t="n">
-        <v>6836367.289100548</v>
+        <v>6836367</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4798,19 +4488,9 @@
           <t>2021-08-04</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4826,12 +4506,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4841,7 +4521,7 @@
         <v>96247287</v>
       </c>
       <c r="B35" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4898,10 +4578,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558710.7366508729</v>
+        <v>558711</v>
       </c>
       <c r="R35" t="n">
-        <v>6836363.645505114</v>
+        <v>6836364</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4931,19 +4611,9 @@
           <t>2021-08-04</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4964,12 +4634,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4979,7 +4649,7 @@
         <v>96247240</v>
       </c>
       <c r="B36" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5024,10 +4694,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558663.4632008653</v>
+        <v>558663</v>
       </c>
       <c r="R36" t="n">
-        <v>6836456.924370303</v>
+        <v>6836457</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5057,19 +4727,9 @@
           <t>2021-08-04</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5085,12 +4745,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5100,7 +4760,7 @@
         <v>96247424</v>
       </c>
       <c r="B37" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5157,10 +4817,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558690.1118572874</v>
+        <v>558690</v>
       </c>
       <c r="R37" t="n">
-        <v>6836317.201947976</v>
+        <v>6836317</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5190,19 +4850,9 @@
           <t>2021-08-29</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5218,12 +4868,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -5233,7 +4883,7 @@
         <v>97205588</v>
       </c>
       <c r="B38" t="n">
-        <v>93044</v>
+        <v>94771</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5274,10 +4924,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558626.5700024338</v>
+        <v>558627</v>
       </c>
       <c r="R38" t="n">
-        <v>6836275.730126046</v>
+        <v>6836276</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5307,19 +4957,9 @@
           <t>2021-11-17</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5335,12 +4975,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5350,7 +4990,7 @@
         <v>97205629</v>
       </c>
       <c r="B39" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5391,10 +5031,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558579.9057241267</v>
+        <v>558580</v>
       </c>
       <c r="R39" t="n">
-        <v>6836165.166850948</v>
+        <v>6836165</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5424,19 +5064,9 @@
           <t>2021-11-17</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5452,12 +5082,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5467,7 +5097,7 @@
         <v>97205682</v>
       </c>
       <c r="B40" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5520,10 +5150,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558675.4619818114</v>
+        <v>558675</v>
       </c>
       <c r="R40" t="n">
-        <v>6836450.951438937</v>
+        <v>6836451</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5553,19 +5183,9 @@
           <t>2021-11-17</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5586,12 +5206,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5601,7 +5221,7 @@
         <v>97205662</v>
       </c>
       <c r="B41" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5654,10 +5274,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558888.4945006571</v>
+        <v>558888</v>
       </c>
       <c r="R41" t="n">
-        <v>6836432.726130273</v>
+        <v>6836433</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5687,19 +5307,9 @@
           <t>2021-11-17</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5720,12 +5330,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5735,7 +5345,7 @@
         <v>97205440</v>
       </c>
       <c r="B42" t="n">
-        <v>56395</v>
+        <v>57481</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5788,10 +5398,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558637.3474665879</v>
+        <v>558637</v>
       </c>
       <c r="R42" t="n">
-        <v>6836397.55935724</v>
+        <v>6836398</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5821,19 +5431,9 @@
           <t>2021-11-17</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -5853,12 +5453,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5868,7 +5468,7 @@
         <v>97981914</v>
       </c>
       <c r="B43" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5921,10 +5521,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558630.8224545156</v>
+        <v>558631</v>
       </c>
       <c r="R43" t="n">
-        <v>6836445.440334397</v>
+        <v>6836445</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5954,19 +5554,9 @@
           <t>2021-08-29</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5987,12 +5577,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -8322,7 +7912,7 @@
         <v>102636359</v>
       </c>
       <c r="B64" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8374,10 +7964,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>558646.4383090814</v>
+        <v>558646</v>
       </c>
       <c r="R64" t="n">
-        <v>6836310.756572842</v>
+        <v>6836311</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -8439,12 +8029,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -8454,7 +8044,7 @@
         <v>102635648</v>
       </c>
       <c r="B65" t="n">
-        <v>89410</v>
+        <v>90975</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8501,10 +8091,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>558700.8508366493</v>
+        <v>558701</v>
       </c>
       <c r="R65" t="n">
-        <v>6836357.299874404</v>
+        <v>6836358</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -8566,12 +8156,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8581,7 +8171,7 @@
         <v>102635248</v>
       </c>
       <c r="B66" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8633,10 +8223,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>558700.65671904</v>
+        <v>558700</v>
       </c>
       <c r="R66" t="n">
-        <v>6836368.700798686</v>
+        <v>6836368</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8698,12 +8288,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8713,7 +8303,7 @@
         <v>102634776</v>
       </c>
       <c r="B67" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8761,10 +8351,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>558683.9539945712</v>
+        <v>558684</v>
       </c>
       <c r="R67" t="n">
-        <v>6836427.337697427</v>
+        <v>6836427</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8821,12 +8411,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8836,7 +8426,7 @@
         <v>102634452</v>
       </c>
       <c r="B68" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8888,10 +8478,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>558668.4227679619</v>
+        <v>558669</v>
       </c>
       <c r="R68" t="n">
-        <v>6836445.129668176</v>
+        <v>6836445</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8948,12 +8538,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8963,7 +8553,7 @@
         <v>103963177</v>
       </c>
       <c r="B69" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9016,10 +8606,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558614.1507402973</v>
+        <v>558614</v>
       </c>
       <c r="R69" t="n">
-        <v>6836306.406033654</v>
+        <v>6836307</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9049,19 +8639,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9087,12 +8667,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -9102,7 +8682,7 @@
         <v>103963705</v>
       </c>
       <c r="B70" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9155,10 +8735,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>558630.4598061274</v>
+        <v>558631</v>
       </c>
       <c r="R70" t="n">
-        <v>6836438.781857147</v>
+        <v>6836439</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9188,19 +8768,9 @@
           <t>2022-09-25</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9226,12 +8796,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -9241,7 +8811,7 @@
         <v>103963368</v>
       </c>
       <c r="B71" t="n">
-        <v>93044</v>
+        <v>94771</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9282,10 +8852,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>558677.4819552574</v>
+        <v>558678</v>
       </c>
       <c r="R71" t="n">
-        <v>6836360.228300998</v>
+        <v>6836360</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9315,19 +8885,9 @@
           <t>2022-09-25</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -9358,12 +8918,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -9373,7 +8933,7 @@
         <v>103963591</v>
       </c>
       <c r="B72" t="n">
-        <v>89392</v>
+        <v>90957</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9421,10 +8981,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>558650.3140795013</v>
+        <v>558650</v>
       </c>
       <c r="R72" t="n">
-        <v>6836390.652346768</v>
+        <v>6836391</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9454,19 +9014,9 @@
           <t>2022-09-25</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -9497,12 +9047,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -9512,7 +9062,7 @@
         <v>103964054</v>
       </c>
       <c r="B73" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9565,10 +9115,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>558665.7703615627</v>
+        <v>558666</v>
       </c>
       <c r="R73" t="n">
-        <v>6836433.205391967</v>
+        <v>6836433</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9598,19 +9148,9 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9636,12 +9176,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -9651,7 +9191,7 @@
         <v>103963470</v>
       </c>
       <c r="B74" t="n">
-        <v>90674</v>
+        <v>92271</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9673,12 +9213,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -9699,10 +9239,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>558658.8556556103</v>
+        <v>558659</v>
       </c>
       <c r="R74" t="n">
-        <v>6836336.152434243</v>
+        <v>6836336</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9732,19 +9272,9 @@
           <t>2022-09-25</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9770,12 +9300,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9785,7 +9315,7 @@
         <v>103963136</v>
       </c>
       <c r="B75" t="n">
-        <v>89832</v>
+        <v>91402</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9837,10 +9367,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>558608.5243126316</v>
+        <v>558608</v>
       </c>
       <c r="R75" t="n">
-        <v>6836217.449925164</v>
+        <v>6836217</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9870,19 +9400,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -9913,12 +9433,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9928,7 +9448,7 @@
         <v>111414049</v>
       </c>
       <c r="B76" t="n">
-        <v>96348</v>
+        <v>98370</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9981,10 +9501,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>558624.5973321907</v>
+        <v>558624</v>
       </c>
       <c r="R76" t="n">
-        <v>6836447.710292835</v>
+        <v>6836447</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -10014,19 +9534,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10042,12 +9552,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -10057,7 +9567,7 @@
         <v>119150694</v>
       </c>
       <c r="B77" t="n">
-        <v>84007</v>
+        <v>84288</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10148,12 +9658,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Jens Hansen, Carina Frost</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -10163,7 +9673,7 @@
         <v>119998685</v>
       </c>
       <c r="B78" t="n">
-        <v>91879</v>
+        <v>92271</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10185,12 +9695,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -10262,12 +9772,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -10277,7 +9787,7 @@
         <v>119996727</v>
       </c>
       <c r="B79" t="n">
-        <v>78542</v>
+        <v>78771</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10376,12 +9886,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -10391,7 +9901,7 @@
         <v>119998328</v>
       </c>
       <c r="B80" t="n">
-        <v>97930</v>
+        <v>98370</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10495,12 +10005,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>88047131</v>
       </c>
       <c r="B2" t="n">
-        <v>90971</v>
+        <v>90977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -794,7 +794,7 @@
         <v>88042293</v>
       </c>
       <c r="B3" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -910,7 +910,7 @@
         <v>88047210</v>
       </c>
       <c r="B4" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,12 +1011,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1026,7 +1026,7 @@
         <v>88046405</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1143,7 +1143,7 @@
         <v>88046755</v>
       </c>
       <c r="B6" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -1373,7 +1373,7 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -1388,7 +1388,7 @@
         <v>88048734</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1619,7 +1619,7 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -1634,7 +1634,7 @@
         <v>88042206</v>
       </c>
       <c r="B10" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -1751,7 +1751,7 @@
         <v>88047659</v>
       </c>
       <c r="B11" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1853,12 +1853,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1868,7 +1868,7 @@
         <v>88047287</v>
       </c>
       <c r="B12" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1970,12 +1970,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1985,7 +1985,7 @@
         <v>88046669</v>
       </c>
       <c r="B13" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -2101,7 +2101,7 @@
         <v>88046386</v>
       </c>
       <c r="B14" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -2217,7 +2217,7 @@
         <v>88046784</v>
       </c>
       <c r="B15" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -2334,7 +2334,7 @@
         <v>88046296</v>
       </c>
       <c r="B16" t="n">
-        <v>91244</v>
+        <v>91250</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -2450,7 +2450,7 @@
         <v>88558798</v>
       </c>
       <c r="B17" t="n">
-        <v>94771</v>
+        <v>94777</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -2557,7 +2557,7 @@
         <v>88559378</v>
       </c>
       <c r="B18" t="n">
-        <v>94771</v>
+        <v>94777</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2649,12 +2649,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2664,7 +2664,7 @@
         <v>88559468</v>
       </c>
       <c r="B19" t="n">
-        <v>94771</v>
+        <v>94777</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2764,12 +2764,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2779,7 +2779,7 @@
         <v>88558994</v>
       </c>
       <c r="B20" t="n">
-        <v>94771</v>
+        <v>94777</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -2886,7 +2886,7 @@
         <v>88558895</v>
       </c>
       <c r="B21" t="n">
-        <v>94771</v>
+        <v>94777</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -2993,7 +2993,7 @@
         <v>88558775</v>
       </c>
       <c r="B22" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -3100,7 +3100,7 @@
         <v>88559291</v>
       </c>
       <c r="B23" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3196,12 +3196,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3211,7 +3211,7 @@
         <v>88559031</v>
       </c>
       <c r="B24" t="n">
-        <v>94771</v>
+        <v>94777</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -3318,7 +3318,7 @@
         <v>88559451</v>
       </c>
       <c r="B25" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3422,12 +3422,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3562,7 +3562,7 @@
         <v>91007790</v>
       </c>
       <c r="B27" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3654,12 +3654,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3669,7 +3669,7 @@
         <v>96247076</v>
       </c>
       <c r="B28" t="n">
-        <v>91166</v>
+        <v>91172</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3773,12 +3773,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3788,7 +3788,7 @@
         <v>96247188</v>
       </c>
       <c r="B29" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3901,12 +3901,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3916,7 +3916,7 @@
         <v>96247391</v>
       </c>
       <c r="B30" t="n">
-        <v>94771</v>
+        <v>94777</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4016,12 +4016,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4031,7 +4031,7 @@
         <v>96247229</v>
       </c>
       <c r="B31" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4140,12 +4140,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4155,7 +4155,7 @@
         <v>96247334</v>
       </c>
       <c r="B32" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4268,12 +4268,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4283,7 +4283,7 @@
         <v>96247262</v>
       </c>
       <c r="B33" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4391,12 +4391,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4406,7 +4406,7 @@
         <v>96247366</v>
       </c>
       <c r="B34" t="n">
-        <v>94771</v>
+        <v>94777</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4506,12 +4506,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4521,7 +4521,7 @@
         <v>96247287</v>
       </c>
       <c r="B35" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4634,12 +4634,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4649,7 +4649,7 @@
         <v>96247240</v>
       </c>
       <c r="B36" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4745,12 +4745,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4760,7 +4760,7 @@
         <v>96247424</v>
       </c>
       <c r="B37" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4868,12 +4868,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4883,7 +4883,7 @@
         <v>97205588</v>
       </c>
       <c r="B38" t="n">
-        <v>94771</v>
+        <v>94777</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4975,12 +4975,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4990,7 +4990,7 @@
         <v>97205629</v>
       </c>
       <c r="B39" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5082,12 +5082,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5097,7 +5097,7 @@
         <v>97205682</v>
       </c>
       <c r="B40" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5206,12 +5206,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5221,7 +5221,7 @@
         <v>97205662</v>
       </c>
       <c r="B41" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5330,12 +5330,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5453,12 +5453,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5468,7 +5468,7 @@
         <v>97981914</v>
       </c>
       <c r="B43" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5577,12 +5577,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -7912,7 +7912,7 @@
         <v>102636359</v>
       </c>
       <c r="B64" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8029,12 +8029,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -8044,7 +8044,7 @@
         <v>102635648</v>
       </c>
       <c r="B65" t="n">
-        <v>90975</v>
+        <v>90981</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8156,12 +8156,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8171,7 +8171,7 @@
         <v>102635248</v>
       </c>
       <c r="B66" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8288,12 +8288,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8303,7 +8303,7 @@
         <v>102634776</v>
       </c>
       <c r="B67" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8411,12 +8411,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8426,7 +8426,7 @@
         <v>102634452</v>
       </c>
       <c r="B68" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8538,12 +8538,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8553,7 +8553,7 @@
         <v>103963177</v>
       </c>
       <c r="B69" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8667,12 +8667,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8682,7 +8682,7 @@
         <v>103963705</v>
       </c>
       <c r="B70" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8796,12 +8796,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8811,7 +8811,7 @@
         <v>103963368</v>
       </c>
       <c r="B71" t="n">
-        <v>94771</v>
+        <v>94777</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8918,12 +8918,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8933,7 +8933,7 @@
         <v>103963591</v>
       </c>
       <c r="B72" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9047,12 +9047,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -9062,7 +9062,7 @@
         <v>103964054</v>
       </c>
       <c r="B73" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9176,12 +9176,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -9191,7 +9191,7 @@
         <v>103963470</v>
       </c>
       <c r="B74" t="n">
-        <v>92271</v>
+        <v>92277</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9300,12 +9300,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9315,7 +9315,7 @@
         <v>103963136</v>
       </c>
       <c r="B75" t="n">
-        <v>91402</v>
+        <v>91408</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9433,12 +9433,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9448,7 +9448,7 @@
         <v>111414049</v>
       </c>
       <c r="B76" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9552,12 +9552,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9567,7 +9567,7 @@
         <v>119150694</v>
       </c>
       <c r="B77" t="n">
-        <v>84288</v>
+        <v>84290</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9658,12 +9658,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Jens Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9673,7 +9673,7 @@
         <v>119998685</v>
       </c>
       <c r="B78" t="n">
-        <v>92271</v>
+        <v>92277</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9772,12 +9772,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9787,7 +9787,7 @@
         <v>119996727</v>
       </c>
       <c r="B79" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9886,12 +9886,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9901,7 +9901,7 @@
         <v>119998328</v>
       </c>
       <c r="B80" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10005,12 +10005,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>88047131</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
+        <v>90980</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>88042293</v>
       </c>
       <c r="B3" t="n">
-        <v>90963</v>
+        <v>90966</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>88047210</v>
       </c>
       <c r="B4" t="n">
-        <v>90963</v>
+        <v>90966</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>88046405</v>
       </c>
       <c r="B5" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>88046755</v>
       </c>
       <c r="B6" t="n">
-        <v>90963</v>
+        <v>90966</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>88048734</v>
       </c>
       <c r="B8" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>88042206</v>
       </c>
       <c r="B10" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>88047659</v>
       </c>
       <c r="B11" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>88047287</v>
       </c>
       <c r="B12" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>88046669</v>
       </c>
       <c r="B13" t="n">
-        <v>90963</v>
+        <v>90966</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>88046386</v>
       </c>
       <c r="B14" t="n">
-        <v>90963</v>
+        <v>90966</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>88046784</v>
       </c>
       <c r="B15" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>88046296</v>
       </c>
       <c r="B16" t="n">
-        <v>91250</v>
+        <v>91253</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>88558798</v>
       </c>
       <c r="B17" t="n">
-        <v>94777</v>
+        <v>94780</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>88559378</v>
       </c>
       <c r="B18" t="n">
-        <v>94777</v>
+        <v>94780</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>88559468</v>
       </c>
       <c r="B19" t="n">
-        <v>94777</v>
+        <v>94780</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>88558994</v>
       </c>
       <c r="B20" t="n">
-        <v>94777</v>
+        <v>94780</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>88558895</v>
       </c>
       <c r="B21" t="n">
-        <v>94777</v>
+        <v>94780</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>88558775</v>
       </c>
       <c r="B22" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>88559291</v>
       </c>
       <c r="B23" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>88559031</v>
       </c>
       <c r="B24" t="n">
-        <v>94777</v>
+        <v>94780</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>88559451</v>
       </c>
       <c r="B25" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>91007790</v>
       </c>
       <c r="B27" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>96247076</v>
       </c>
       <c r="B28" t="n">
-        <v>91172</v>
+        <v>91175</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>96247188</v>
       </c>
       <c r="B29" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>96247391</v>
       </c>
       <c r="B30" t="n">
-        <v>94777</v>
+        <v>94780</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>96247229</v>
       </c>
       <c r="B31" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>96247334</v>
       </c>
       <c r="B32" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>96247262</v>
       </c>
       <c r="B33" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>96247366</v>
       </c>
       <c r="B34" t="n">
-        <v>94777</v>
+        <v>94780</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>96247287</v>
       </c>
       <c r="B35" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>96247240</v>
       </c>
       <c r="B36" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>96247424</v>
       </c>
       <c r="B37" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>97205588</v>
       </c>
       <c r="B38" t="n">
-        <v>94777</v>
+        <v>94780</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>97205629</v>
       </c>
       <c r="B39" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>97205682</v>
       </c>
       <c r="B40" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         <v>97205662</v>
       </c>
       <c r="B41" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>97981914</v>
       </c>
       <c r="B43" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>102636359</v>
       </c>
       <c r="B64" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         <v>102635648</v>
       </c>
       <c r="B65" t="n">
-        <v>90981</v>
+        <v>90984</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>102635248</v>
       </c>
       <c r="B66" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>102634776</v>
       </c>
       <c r="B67" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>102634452</v>
       </c>
       <c r="B68" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>103963177</v>
       </c>
       <c r="B69" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>103963705</v>
       </c>
       <c r="B70" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>103963368</v>
       </c>
       <c r="B71" t="n">
-        <v>94777</v>
+        <v>94780</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>103963591</v>
       </c>
       <c r="B72" t="n">
-        <v>90963</v>
+        <v>90966</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>103964054</v>
       </c>
       <c r="B73" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>103963470</v>
       </c>
       <c r="B74" t="n">
-        <v>92277</v>
+        <v>92280</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>103963136</v>
       </c>
       <c r="B75" t="n">
-        <v>91408</v>
+        <v>91411</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>111414049</v>
       </c>
       <c r="B76" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>119150694</v>
       </c>
       <c r="B77" t="n">
-        <v>84290</v>
+        <v>84293</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Jens Hansen, Carina Frost</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9673,7 +9673,7 @@
         <v>119998685</v>
       </c>
       <c r="B78" t="n">
-        <v>92277</v>
+        <v>92280</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>119996727</v>
       </c>
       <c r="B79" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>119998328</v>
       </c>
       <c r="B80" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>88047131</v>
       </c>
       <c r="B2" t="n">
-        <v>90980</v>
+        <v>90997</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>88042293</v>
       </c>
       <c r="B3" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>88047210</v>
       </c>
       <c r="B4" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>88046405</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>88046755</v>
       </c>
       <c r="B6" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>88042353</v>
       </c>
       <c r="B7" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>88048734</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>88046342</v>
       </c>
       <c r="B9" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>88042206</v>
       </c>
       <c r="B10" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>88047659</v>
       </c>
       <c r="B11" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>88047287</v>
       </c>
       <c r="B12" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>88046669</v>
       </c>
       <c r="B13" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>88046386</v>
       </c>
       <c r="B14" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>88046784</v>
       </c>
       <c r="B15" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>88046296</v>
       </c>
       <c r="B16" t="n">
-        <v>91253</v>
+        <v>91270</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>88558798</v>
       </c>
       <c r="B17" t="n">
-        <v>94780</v>
+        <v>94797</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>88559378</v>
       </c>
       <c r="B18" t="n">
-        <v>94780</v>
+        <v>94797</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>88559468</v>
       </c>
       <c r="B19" t="n">
-        <v>94780</v>
+        <v>94797</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>88558994</v>
       </c>
       <c r="B20" t="n">
-        <v>94780</v>
+        <v>94797</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>88558895</v>
       </c>
       <c r="B21" t="n">
-        <v>94780</v>
+        <v>94797</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>88558775</v>
       </c>
       <c r="B22" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>88559291</v>
       </c>
       <c r="B23" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>88559031</v>
       </c>
       <c r="B24" t="n">
-        <v>94780</v>
+        <v>94797</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>88559451</v>
       </c>
       <c r="B25" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>91007790</v>
       </c>
       <c r="B27" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>96247076</v>
       </c>
       <c r="B28" t="n">
-        <v>91175</v>
+        <v>91192</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>96247188</v>
       </c>
       <c r="B29" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>96247391</v>
       </c>
       <c r="B30" t="n">
-        <v>94780</v>
+        <v>94797</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>96247229</v>
       </c>
       <c r="B31" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>96247334</v>
       </c>
       <c r="B32" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>96247262</v>
       </c>
       <c r="B33" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>96247366</v>
       </c>
       <c r="B34" t="n">
-        <v>94780</v>
+        <v>94797</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>96247287</v>
       </c>
       <c r="B35" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>96247240</v>
       </c>
       <c r="B36" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>96247424</v>
       </c>
       <c r="B37" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>97205588</v>
       </c>
       <c r="B38" t="n">
-        <v>94780</v>
+        <v>94797</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>97205629</v>
       </c>
       <c r="B39" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>97205682</v>
       </c>
       <c r="B40" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         <v>97205662</v>
       </c>
       <c r="B41" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>97205440</v>
       </c>
       <c r="B42" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>97981914</v>
       </c>
       <c r="B43" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>102636359</v>
       </c>
       <c r="B64" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         <v>102635648</v>
       </c>
       <c r="B65" t="n">
-        <v>90984</v>
+        <v>91001</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>102635248</v>
       </c>
       <c r="B66" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>102634776</v>
       </c>
       <c r="B67" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>102634452</v>
       </c>
       <c r="B68" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>103963177</v>
       </c>
       <c r="B69" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>103963705</v>
       </c>
       <c r="B70" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>103963368</v>
       </c>
       <c r="B71" t="n">
-        <v>94780</v>
+        <v>94797</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>103963591</v>
       </c>
       <c r="B72" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>103964054</v>
       </c>
       <c r="B73" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>103963470</v>
       </c>
       <c r="B74" t="n">
-        <v>92280</v>
+        <v>92297</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>103963136</v>
       </c>
       <c r="B75" t="n">
-        <v>91411</v>
+        <v>91428</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>111414049</v>
       </c>
       <c r="B76" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>119150694</v>
       </c>
       <c r="B77" t="n">
-        <v>84293</v>
+        <v>84289</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>119998685</v>
       </c>
       <c r="B78" t="n">
-        <v>92280</v>
+        <v>92297</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>119996727</v>
       </c>
       <c r="B79" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>119998328</v>
       </c>
       <c r="B80" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>88047131</v>
       </c>
       <c r="B2" t="n">
-        <v>90997</v>
+        <v>91002</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>88042293</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>88047210</v>
       </c>
       <c r="B4" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>88046405</v>
       </c>
       <c r="B5" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>88046755</v>
       </c>
       <c r="B6" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>88042353</v>
       </c>
       <c r="B7" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>88048734</v>
       </c>
       <c r="B8" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>88046342</v>
       </c>
       <c r="B9" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>88042206</v>
       </c>
       <c r="B10" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>88047659</v>
       </c>
       <c r="B11" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>88047287</v>
       </c>
       <c r="B12" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>88046669</v>
       </c>
       <c r="B13" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>88046386</v>
       </c>
       <c r="B14" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>88046784</v>
       </c>
       <c r="B15" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>88046296</v>
       </c>
       <c r="B16" t="n">
-        <v>91270</v>
+        <v>91275</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>88558798</v>
       </c>
       <c r="B17" t="n">
-        <v>94797</v>
+        <v>94803</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>88559378</v>
       </c>
       <c r="B18" t="n">
-        <v>94797</v>
+        <v>94803</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>88559468</v>
       </c>
       <c r="B19" t="n">
-        <v>94797</v>
+        <v>94803</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>88558994</v>
       </c>
       <c r="B20" t="n">
-        <v>94797</v>
+        <v>94803</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>88558895</v>
       </c>
       <c r="B21" t="n">
-        <v>94797</v>
+        <v>94803</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>88558775</v>
       </c>
       <c r="B22" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>88559291</v>
       </c>
       <c r="B23" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>88559031</v>
       </c>
       <c r="B24" t="n">
-        <v>94797</v>
+        <v>94803</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>88559451</v>
       </c>
       <c r="B25" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>91007790</v>
       </c>
       <c r="B27" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>96247076</v>
       </c>
       <c r="B28" t="n">
-        <v>91192</v>
+        <v>91197</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>96247188</v>
       </c>
       <c r="B29" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>96247391</v>
       </c>
       <c r="B30" t="n">
-        <v>94797</v>
+        <v>94803</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>96247229</v>
       </c>
       <c r="B31" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>96247334</v>
       </c>
       <c r="B32" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>96247262</v>
       </c>
       <c r="B33" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>96247366</v>
       </c>
       <c r="B34" t="n">
-        <v>94797</v>
+        <v>94803</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>96247287</v>
       </c>
       <c r="B35" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>96247240</v>
       </c>
       <c r="B36" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>96247424</v>
       </c>
       <c r="B37" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>97205588</v>
       </c>
       <c r="B38" t="n">
-        <v>94797</v>
+        <v>94803</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>97205629</v>
       </c>
       <c r="B39" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>97205682</v>
       </c>
       <c r="B40" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         <v>97205662</v>
       </c>
       <c r="B41" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>97205440</v>
       </c>
       <c r="B42" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>97981914</v>
       </c>
       <c r="B43" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>102636359</v>
       </c>
       <c r="B64" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         <v>102635648</v>
       </c>
       <c r="B65" t="n">
-        <v>91001</v>
+        <v>91006</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>102635248</v>
       </c>
       <c r="B66" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>102634776</v>
       </c>
       <c r="B67" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>102634452</v>
       </c>
       <c r="B68" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>103963177</v>
       </c>
       <c r="B69" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>103963705</v>
       </c>
       <c r="B70" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>103963368</v>
       </c>
       <c r="B71" t="n">
-        <v>94797</v>
+        <v>94803</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>103963591</v>
       </c>
       <c r="B72" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>103964054</v>
       </c>
       <c r="B73" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>103963470</v>
       </c>
       <c r="B74" t="n">
-        <v>92297</v>
+        <v>92302</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>103963136</v>
       </c>
       <c r="B75" t="n">
-        <v>91428</v>
+        <v>91433</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>111414049</v>
       </c>
       <c r="B76" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>119150694</v>
       </c>
       <c r="B77" t="n">
-        <v>84289</v>
+        <v>84294</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Jens Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9673,7 +9673,7 @@
         <v>119998685</v>
       </c>
       <c r="B78" t="n">
-        <v>92297</v>
+        <v>92302</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>119996727</v>
       </c>
       <c r="B79" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>119998328</v>
       </c>
       <c r="B80" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>88047131</v>
       </c>
       <c r="B2" t="n">
-        <v>91002</v>
+        <v>91004</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>88042293</v>
       </c>
       <c r="B3" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>88047210</v>
       </c>
       <c r="B4" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>88046405</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>88046755</v>
       </c>
       <c r="B6" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>88042353</v>
       </c>
       <c r="B7" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>88048734</v>
       </c>
       <c r="B8" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>88046342</v>
       </c>
       <c r="B9" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>88042206</v>
       </c>
       <c r="B10" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>88047659</v>
       </c>
       <c r="B11" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>88047287</v>
       </c>
       <c r="B12" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>88046669</v>
       </c>
       <c r="B13" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>88046386</v>
       </c>
       <c r="B14" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>88046784</v>
       </c>
       <c r="B15" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>88046296</v>
       </c>
       <c r="B16" t="n">
-        <v>91275</v>
+        <v>91277</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>88558798</v>
       </c>
       <c r="B17" t="n">
-        <v>94803</v>
+        <v>94805</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>88559378</v>
       </c>
       <c r="B18" t="n">
-        <v>94803</v>
+        <v>94805</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>88559468</v>
       </c>
       <c r="B19" t="n">
-        <v>94803</v>
+        <v>94805</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>88558994</v>
       </c>
       <c r="B20" t="n">
-        <v>94803</v>
+        <v>94805</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>88558895</v>
       </c>
       <c r="B21" t="n">
-        <v>94803</v>
+        <v>94805</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>88558775</v>
       </c>
       <c r="B22" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>88559291</v>
       </c>
       <c r="B23" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>88559031</v>
       </c>
       <c r="B24" t="n">
-        <v>94803</v>
+        <v>94805</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>88559451</v>
       </c>
       <c r="B25" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>91007790</v>
       </c>
       <c r="B27" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>96247076</v>
       </c>
       <c r="B28" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>96247188</v>
       </c>
       <c r="B29" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>96247391</v>
       </c>
       <c r="B30" t="n">
-        <v>94803</v>
+        <v>94805</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>96247229</v>
       </c>
       <c r="B31" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>96247334</v>
       </c>
       <c r="B32" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>96247262</v>
       </c>
       <c r="B33" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>96247366</v>
       </c>
       <c r="B34" t="n">
-        <v>94803</v>
+        <v>94805</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>96247287</v>
       </c>
       <c r="B35" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>96247240</v>
       </c>
       <c r="B36" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>96247424</v>
       </c>
       <c r="B37" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>97205588</v>
       </c>
       <c r="B38" t="n">
-        <v>94803</v>
+        <v>94805</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>97205629</v>
       </c>
       <c r="B39" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>97205682</v>
       </c>
       <c r="B40" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         <v>97205662</v>
       </c>
       <c r="B41" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>97205440</v>
       </c>
       <c r="B42" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>97981914</v>
       </c>
       <c r="B43" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>102636359</v>
       </c>
       <c r="B64" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         <v>102635648</v>
       </c>
       <c r="B65" t="n">
-        <v>91006</v>
+        <v>91008</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>102635248</v>
       </c>
       <c r="B66" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>102634776</v>
       </c>
       <c r="B67" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>102634452</v>
       </c>
       <c r="B68" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>103963177</v>
       </c>
       <c r="B69" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>103963705</v>
       </c>
       <c r="B70" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>103963368</v>
       </c>
       <c r="B71" t="n">
-        <v>94803</v>
+        <v>94805</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>103963591</v>
       </c>
       <c r="B72" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>103964054</v>
       </c>
       <c r="B73" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>103963470</v>
       </c>
       <c r="B74" t="n">
-        <v>92302</v>
+        <v>92304</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>103963136</v>
       </c>
       <c r="B75" t="n">
-        <v>91433</v>
+        <v>91435</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>111414049</v>
       </c>
       <c r="B76" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>119150694</v>
       </c>
       <c r="B77" t="n">
-        <v>84294</v>
+        <v>84296</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Jens Hansen, Carina Frost</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9673,7 +9673,7 @@
         <v>119998685</v>
       </c>
       <c r="B78" t="n">
-        <v>92302</v>
+        <v>92304</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>119996727</v>
       </c>
       <c r="B79" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>119998328</v>
       </c>
       <c r="B80" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>88046405</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>88048734</v>
       </c>
       <c r="B8" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jens Hansen</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1634,7 +1634,7 @@
         <v>88042206</v>
       </c>
       <c r="B10" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>88047659</v>
       </c>
       <c r="B11" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>88047287</v>
       </c>
       <c r="B12" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>88046784</v>
       </c>
       <c r="B15" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>88558798</v>
       </c>
       <c r="B17" t="n">
-        <v>94805</v>
+        <v>95313</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jens Hansen</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2557,7 +2557,7 @@
         <v>88559378</v>
       </c>
       <c r="B18" t="n">
-        <v>94805</v>
+        <v>95313</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>88559468</v>
       </c>
       <c r="B19" t="n">
-        <v>94805</v>
+        <v>95313</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>88558994</v>
       </c>
       <c r="B20" t="n">
-        <v>94805</v>
+        <v>95313</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jens Hansen</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2886,7 +2886,7 @@
         <v>88558895</v>
       </c>
       <c r="B21" t="n">
-        <v>94805</v>
+        <v>95313</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jens Hansen</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2993,7 +2993,7 @@
         <v>88558775</v>
       </c>
       <c r="B22" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jens Hansen</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3100,7 +3100,7 @@
         <v>88559291</v>
       </c>
       <c r="B23" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>88559031</v>
       </c>
       <c r="B24" t="n">
-        <v>94805</v>
+        <v>95313</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jens Hansen</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3318,7 +3318,7 @@
         <v>88559451</v>
       </c>
       <c r="B25" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>91007790</v>
       </c>
       <c r="B27" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>96247188</v>
       </c>
       <c r="B29" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>96247391</v>
       </c>
       <c r="B30" t="n">
-        <v>94805</v>
+        <v>95313</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>96247229</v>
       </c>
       <c r="B31" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>96247334</v>
       </c>
       <c r="B32" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>96247262</v>
       </c>
       <c r="B33" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>96247366</v>
       </c>
       <c r="B34" t="n">
-        <v>94805</v>
+        <v>95313</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>96247287</v>
       </c>
       <c r="B35" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>96247240</v>
       </c>
       <c r="B36" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>96247424</v>
       </c>
       <c r="B37" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>97205588</v>
       </c>
       <c r="B38" t="n">
-        <v>94805</v>
+        <v>95313</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>97205629</v>
       </c>
       <c r="B39" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>97205682</v>
       </c>
       <c r="B40" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         <v>97205662</v>
       </c>
       <c r="B41" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>97981914</v>
       </c>
       <c r="B43" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>102636359</v>
       </c>
       <c r="B64" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>102635248</v>
       </c>
       <c r="B66" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>102634776</v>
       </c>
       <c r="B67" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>102634452</v>
       </c>
       <c r="B68" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>103963177</v>
       </c>
       <c r="B69" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>103963705</v>
       </c>
       <c r="B70" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>103963368</v>
       </c>
       <c r="B71" t="n">
-        <v>94805</v>
+        <v>95313</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>103964054</v>
       </c>
       <c r="B73" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>111414049</v>
       </c>
       <c r="B76" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9901,7 +9901,7 @@
         <v>119998328</v>
       </c>
       <c r="B80" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY80"/>
+  <dimension ref="A1:AY87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10015,6 +10015,753 @@
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>127897063</v>
+      </c>
+      <c r="B81" t="n">
+        <v>98490</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Nyboberget Hamre 4:26, Hls</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>558628</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6836235</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>2 blommande</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Jenss Hansen, Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>127897354</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57660</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Nyboberget Hamre 4:26, Hls</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>558628</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6836235</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Jenss Hansen, Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>127896060</v>
+      </c>
+      <c r="B83" t="n">
+        <v>91338</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Nyboberget Hamre 4:26, Hls</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>558655</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6836406</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>127896731</v>
+      </c>
+      <c r="B84" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Nyboberget Hamre 4:26, Hls</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>558628</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6836270</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Jenss Hansen, Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>127897321</v>
+      </c>
+      <c r="B85" t="n">
+        <v>95688</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Nyboberget Hamre 4:26, Hls</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>558628</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6836235</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Jenss Hansen, Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>127896396</v>
+      </c>
+      <c r="B86" t="n">
+        <v>91338</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Nyboberget Hamre 4:26, Hls</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>558646</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6836314</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>127897152</v>
+      </c>
+      <c r="B87" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Nyboberget Hamre 4:26, Hls</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>558628</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6836235</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Jenss Hansen, Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10017,46 +10017,38 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127897063</v>
+        <v>127897354</v>
       </c>
       <c r="B81" t="n">
-        <v>98490</v>
+        <v>57663</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -10102,18 +10094,12 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>2 blommande</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -10132,38 +10118,46 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127897354</v>
+        <v>127897063</v>
       </c>
       <c r="B82" t="n">
-        <v>57660</v>
+        <v>98493</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -10209,12 +10203,18 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>2 blommande</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -10236,7 +10236,7 @@
         <v>127896060</v>
       </c>
       <c r="B83" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>127896731</v>
       </c>
       <c r="B84" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>127897321</v>
       </c>
       <c r="B85" t="n">
-        <v>95688</v>
+        <v>95691</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>127896396</v>
       </c>
       <c r="B86" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>127897152</v>
       </c>
       <c r="B87" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10020,7 +10020,7 @@
         <v>127897354</v>
       </c>
       <c r="B81" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>127897063</v>
       </c>
       <c r="B82" t="n">
-        <v>98493</v>
+        <v>98501</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>127896060</v>
       </c>
       <c r="B83" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>127896731</v>
       </c>
       <c r="B84" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>127897321</v>
       </c>
       <c r="B85" t="n">
-        <v>95691</v>
+        <v>95699</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>127896396</v>
       </c>
       <c r="B86" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>127897152</v>
       </c>
       <c r="B87" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10121,7 +10121,7 @@
         <v>127897063</v>
       </c>
       <c r="B82" t="n">
-        <v>98501</v>
+        <v>98502</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10233,37 +10233,46 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127896060</v>
+        <v>127896731</v>
       </c>
       <c r="B83" t="n">
-        <v>91349</v>
+        <v>98468</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -10271,10 +10280,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>558655</v>
+        <v>558628</v>
       </c>
       <c r="R83" t="n">
-        <v>6836406</v>
+        <v>6836270</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10319,21 +10328,6 @@
       <c r="AG83" t="b">
         <v>0</v>
       </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
@@ -10342,53 +10336,44 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127896731</v>
+        <v>127896060</v>
       </c>
       <c r="B84" t="n">
-        <v>98467</v>
+        <v>91350</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -10396,10 +10381,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>558628</v>
+        <v>558655</v>
       </c>
       <c r="R84" t="n">
-        <v>6836270</v>
+        <v>6836406</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -10444,6 +10429,21 @@
       <c r="AG84" t="b">
         <v>0</v>
       </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -10462,7 +10462,7 @@
         <v>127897321</v>
       </c>
       <c r="B85" t="n">
-        <v>95699</v>
+        <v>95700</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>127896396</v>
       </c>
       <c r="B86" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>127897152</v>
       </c>
       <c r="B87" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10017,38 +10017,46 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127897354</v>
+        <v>127897063</v>
       </c>
       <c r="B81" t="n">
-        <v>57669</v>
+        <v>98502</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -10094,12 +10102,18 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>2 blommande</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -10118,46 +10132,38 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127897063</v>
+        <v>127897354</v>
       </c>
       <c r="B82" t="n">
-        <v>98502</v>
+        <v>57669</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -10203,18 +10209,12 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>2 blommande</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10017,46 +10017,38 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127897063</v>
+        <v>127897354</v>
       </c>
       <c r="B81" t="n">
-        <v>98502</v>
+        <v>57669</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -10102,18 +10094,12 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>2 blommande</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -10132,38 +10118,46 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127897354</v>
+        <v>127897063</v>
       </c>
       <c r="B82" t="n">
-        <v>57669</v>
+        <v>98503</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -10209,12 +10203,18 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>2 blommande</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -10226,53 +10226,44 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127896731</v>
+        <v>127896060</v>
       </c>
       <c r="B83" t="n">
-        <v>98468</v>
+        <v>91351</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -10280,10 +10271,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>558628</v>
+        <v>558655</v>
       </c>
       <c r="R83" t="n">
-        <v>6836270</v>
+        <v>6836406</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10328,6 +10319,21 @@
       <c r="AG83" t="b">
         <v>0</v>
       </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
@@ -10336,44 +10342,53 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127896060</v>
+        <v>127896731</v>
       </c>
       <c r="B84" t="n">
-        <v>91350</v>
+        <v>98469</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -10381,10 +10396,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>558655</v>
+        <v>558628</v>
       </c>
       <c r="R84" t="n">
-        <v>6836406</v>
+        <v>6836270</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -10429,21 +10444,6 @@
       <c r="AG84" t="b">
         <v>0</v>
       </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -10462,7 +10462,7 @@
         <v>127897321</v>
       </c>
       <c r="B85" t="n">
-        <v>95700</v>
+        <v>95701</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>127896396</v>
       </c>
       <c r="B86" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>127897152</v>
       </c>
       <c r="B87" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10121,7 +10121,7 @@
         <v>127897063</v>
       </c>
       <c r="B82" t="n">
-        <v>98503</v>
+        <v>98504</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -10236,7 +10236,7 @@
         <v>127896060</v>
       </c>
       <c r="B83" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>127896731</v>
       </c>
       <c r="B84" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -10462,7 +10462,7 @@
         <v>127897321</v>
       </c>
       <c r="B85" t="n">
-        <v>95701</v>
+        <v>95702</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>127896396</v>
       </c>
       <c r="B86" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>127897152</v>
       </c>
       <c r="B87" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10233,37 +10233,46 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127896060</v>
+        <v>127896731</v>
       </c>
       <c r="B83" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -10271,10 +10280,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>558655</v>
+        <v>558628</v>
       </c>
       <c r="R83" t="n">
-        <v>6836406</v>
+        <v>6836270</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10319,21 +10328,6 @@
       <c r="AG83" t="b">
         <v>0</v>
       </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
@@ -10342,53 +10336,44 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127896731</v>
+        <v>127896060</v>
       </c>
       <c r="B84" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -10396,10 +10381,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>558628</v>
+        <v>558655</v>
       </c>
       <c r="R84" t="n">
-        <v>6836270</v>
+        <v>6836406</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -10444,6 +10429,21 @@
       <c r="AG84" t="b">
         <v>0</v>
       </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY87"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10762,6 +10762,436 @@
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>128358533</v>
+      </c>
+      <c r="B88" t="n">
+        <v>95705</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Nyboberget Hamre 4:31, Hls</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>558676</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6836405</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>128358881</v>
+      </c>
+      <c r="B89" t="n">
+        <v>84605</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>5589</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Rödbrun klubbdyna</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Trichoderma nybergianum</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Nyboberget Hamre 4:31, Hls</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>558631</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6836248</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Jenss Hansen, Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>128358906</v>
+      </c>
+      <c r="B90" t="n">
+        <v>92052</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Nyboberget Hamre 4:31, Hls</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>558684</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6836342</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Jenss Hansen, Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>128358565</v>
+      </c>
+      <c r="B91" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Nyboberget Hamre 4:31, Hls</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>558693</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6836432</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10020,7 +10020,7 @@
         <v>127897354</v>
       </c>
       <c r="B81" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -10121,7 +10121,7 @@
         <v>127897063</v>
       </c>
       <c r="B82" t="n">
-        <v>98504</v>
+        <v>98512</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10226,53 +10226,44 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127896731</v>
+        <v>127896060</v>
       </c>
       <c r="B83" t="n">
-        <v>98470</v>
+        <v>91360</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -10280,10 +10271,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>558628</v>
+        <v>558655</v>
       </c>
       <c r="R83" t="n">
-        <v>6836270</v>
+        <v>6836406</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10328,6 +10319,21 @@
       <c r="AG83" t="b">
         <v>0</v>
       </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
@@ -10336,44 +10342,53 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127896060</v>
+        <v>127896731</v>
       </c>
       <c r="B84" t="n">
-        <v>91352</v>
+        <v>98478</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -10381,10 +10396,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>558655</v>
+        <v>558628</v>
       </c>
       <c r="R84" t="n">
-        <v>6836406</v>
+        <v>6836270</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -10429,21 +10444,6 @@
       <c r="AG84" t="b">
         <v>0</v>
       </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -10462,7 +10462,7 @@
         <v>127897321</v>
       </c>
       <c r="B85" t="n">
-        <v>95702</v>
+        <v>95710</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10564,7 +10564,7 @@
         <v>127896396</v>
       </c>
       <c r="B86" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>127897152</v>
       </c>
       <c r="B87" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10767,7 +10767,7 @@
         <v>128358533</v>
       </c>
       <c r="B88" t="n">
-        <v>95705</v>
+        <v>95710</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>128358881</v>
       </c>
       <c r="B89" t="n">
-        <v>84605</v>
+        <v>84606</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>128358906</v>
       </c>
       <c r="B90" t="n">
-        <v>92052</v>
+        <v>92057</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>128358565</v>
       </c>
       <c r="B91" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10017,38 +10017,46 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127897354</v>
+        <v>127897063</v>
       </c>
       <c r="B81" t="n">
-        <v>57670</v>
+        <v>98512</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -10094,12 +10102,18 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>2 blommande</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -10118,46 +10132,38 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127897063</v>
+        <v>127897354</v>
       </c>
       <c r="B82" t="n">
-        <v>98512</v>
+        <v>57670</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -10203,18 +10209,12 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>2 blommande</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10017,46 +10017,38 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127897063</v>
+        <v>127897354</v>
       </c>
       <c r="B81" t="n">
-        <v>98512</v>
+        <v>57682</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -10102,18 +10094,12 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>2 blommande</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -10125,45 +10111,53 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127897354</v>
+        <v>127897063</v>
       </c>
       <c r="B82" t="n">
-        <v>57670</v>
+        <v>98605</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -10209,12 +10203,18 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>2 blommande</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -10236,7 +10236,7 @@
         <v>127896060</v>
       </c>
       <c r="B83" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>127896731</v>
       </c>
       <c r="B84" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -10462,7 +10462,7 @@
         <v>127897321</v>
       </c>
       <c r="B85" t="n">
-        <v>95710</v>
+        <v>95803</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10564,7 +10564,7 @@
         <v>127896396</v>
       </c>
       <c r="B86" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>127897152</v>
       </c>
       <c r="B87" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10767,7 +10767,7 @@
         <v>128358533</v>
       </c>
       <c r="B88" t="n">
-        <v>95710</v>
+        <v>95803</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>128358881</v>
       </c>
       <c r="B89" t="n">
-        <v>84606</v>
+        <v>84690</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -10978,7 +10978,7 @@
         <v>128358906</v>
       </c>
       <c r="B90" t="n">
-        <v>92057</v>
+        <v>92149</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -11087,7 +11087,7 @@
         <v>128358565</v>
       </c>
       <c r="B91" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10968,7 +10968,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -11077,7 +11077,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10017,38 +10017,46 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127897354</v>
+        <v>127897063</v>
       </c>
       <c r="B81" t="n">
-        <v>57682</v>
+        <v>98605</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -10094,12 +10102,18 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>2 blommande</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -10118,46 +10132,38 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127897063</v>
+        <v>127897354</v>
       </c>
       <c r="B82" t="n">
-        <v>98605</v>
+        <v>57682</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -10203,18 +10209,12 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>2 blommande</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10020,7 +10020,7 @@
         <v>127897063</v>
       </c>
       <c r="B81" t="n">
-        <v>98605</v>
+        <v>98619</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         <v>127897354</v>
       </c>
       <c r="B82" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>127896060</v>
       </c>
       <c r="B83" t="n">
-        <v>91452</v>
+        <v>91464</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>127896731</v>
       </c>
       <c r="B84" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>127897321</v>
       </c>
       <c r="B85" t="n">
-        <v>95803</v>
+        <v>95815</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>127896396</v>
       </c>
       <c r="B86" t="n">
-        <v>91452</v>
+        <v>91464</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>127897152</v>
       </c>
       <c r="B87" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>128358533</v>
       </c>
       <c r="B88" t="n">
-        <v>95803</v>
+        <v>95815</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>128358881</v>
       </c>
       <c r="B89" t="n">
-        <v>84690</v>
+        <v>84694</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>128358906</v>
       </c>
       <c r="B90" t="n">
-        <v>92149</v>
+        <v>92161</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>128358565</v>
       </c>
       <c r="B91" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10767,7 +10767,7 @@
         <v>128358533</v>
       </c>
       <c r="B88" t="n">
-        <v>95815</v>
+        <v>95817</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>128358881</v>
       </c>
       <c r="B89" t="n">
-        <v>84694</v>
+        <v>84696</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>128358906</v>
       </c>
       <c r="B90" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>128358565</v>
       </c>
       <c r="B91" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -11087,7 +11087,7 @@
         <v>128358565</v>
       </c>
       <c r="B91" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10767,7 +10767,7 @@
         <v>128358533</v>
       </c>
       <c r="B88" t="n">
-        <v>95817</v>
+        <v>95818</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -10978,7 +10978,7 @@
         <v>128358906</v>
       </c>
       <c r="B90" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -11087,7 +11087,7 @@
         <v>128358565</v>
       </c>
       <c r="B91" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10767,7 +10767,7 @@
         <v>128358533</v>
       </c>
       <c r="B88" t="n">
-        <v>95818</v>
+        <v>95845</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>128358881</v>
       </c>
       <c r="B89" t="n">
-        <v>84696</v>
+        <v>84723</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>128358906</v>
       </c>
       <c r="B90" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>128358565</v>
       </c>
       <c r="B91" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10767,7 +10767,7 @@
         <v>128358533</v>
       </c>
       <c r="B88" t="n">
-        <v>95845</v>
+        <v>95858</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>128358881</v>
       </c>
       <c r="B89" t="n">
-        <v>84723</v>
+        <v>84727</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>128358906</v>
       </c>
       <c r="B90" t="n">
-        <v>92191</v>
+        <v>92201</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>128358565</v>
       </c>
       <c r="B91" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -10767,7 +10767,7 @@
         <v>128358533</v>
       </c>
       <c r="B88" t="n">
-        <v>95858</v>
+        <v>95862</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>128358881</v>
       </c>
       <c r="B89" t="n">
-        <v>84727</v>
+        <v>84731</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>128358906</v>
       </c>
       <c r="B90" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>128358565</v>
       </c>
       <c r="B91" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 48020-2021 artfynd.xlsx
+++ b/artfynd/A 48020-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY108"/>
+  <dimension ref="A1:AZ108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88259688</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88256009</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88046296</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96247076</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1233,6 +1258,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88042293</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88046386</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1455,6 +1490,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88046669</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1566,6 +1606,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88046755</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1677,6 +1722,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88047210</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1801,6 +1851,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103963591</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1908,6 +1963,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119954832</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2024,6 +2084,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127896060</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2125,6 +2190,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127896396</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2236,6 +2306,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88047131</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2347,6 +2422,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88550222</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2475,6 +2555,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103963136</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2577,6 +2662,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88558798</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2679,6 +2769,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88558855</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2781,6 +2876,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88558895</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2883,6 +2983,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88558994</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2985,6 +3090,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88559031</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3087,6 +3197,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88559378</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3197,6 +3312,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88559468</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3307,6 +3427,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96247366</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3417,6 +3542,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96247391</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3532,6 +3662,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97205567</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3634,6 +3769,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97205602</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3751,6 +3891,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103963368</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3853,6 +3998,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127897321</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3955,6 +4105,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128358533</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4071,6 +4226,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118743471</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4180,6 +4340,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128358906</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4281,6 +4446,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150694</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4390,6 +4560,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128358881</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4509,6 +4684,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103963470</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4618,6 +4798,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119998685</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4727,6 +4912,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119996727</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4851,6 +5041,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88042353</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4975,6 +5170,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88046342</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5076,6 +5276,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127897354</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5194,6 +5399,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97205440</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5309,6 +5519,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127897063</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5421,6 +5636,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88042206</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5533,6 +5753,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88046405</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5645,6 +5870,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88046784</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5757,6 +5987,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88046957</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5869,6 +6104,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88047045</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5971,6 +6211,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88047065</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6083,6 +6328,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88047094</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6195,6 +6445,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88047287</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6307,6 +6562,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88047659</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6419,6 +6679,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88048734</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6521,6 +6786,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88558775</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6627,6 +6897,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88559291</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6741,6 +7016,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88559451</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6843,6 +7123,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91007790</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6966,6 +7251,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96247188</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7085,6 +7375,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96247229</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7191,6 +7486,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96247240</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7309,6 +7609,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96247262</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7432,6 +7737,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96247287</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7555,6 +7865,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96247334</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7673,6 +7988,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96247424</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7792,6 +8112,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97205622</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7894,6 +8219,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97205629</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8013,6 +8343,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97205662</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8132,6 +8467,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97205682</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8251,6 +8591,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97981914</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8352,6 +8697,11 @@
           <t>Järvsö Knärotinventering</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98452155</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8453,6 +8803,11 @@
           <t>Järvsö Knärotinventering</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98452156</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8554,6 +8909,11 @@
           <t>Järvsö Knärotinventering</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98452157</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8655,6 +9015,11 @@
           <t>Järvsö Knärotinventering</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98452158</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8756,6 +9121,11 @@
           <t>Järvsö Knärotinventering</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98452159</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8857,6 +9227,11 @@
           <t>Järvsö Knärotinventering</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98452160</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8958,6 +9333,11 @@
           <t>Järvsö Knärotinventering</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98452161</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9059,6 +9439,11 @@
           <t>Järvsö Knärotinventering</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98452162</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9160,6 +9545,11 @@
           <t>Järvsö Knärotinventering</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98452163</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9261,6 +9651,11 @@
           <t>Järvsö Knärotinventering</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98452164</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9362,6 +9757,11 @@
           <t>Järvsö Knärotinventering</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98452165</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9463,6 +9863,11 @@
           <t>Järvsö Knärotinventering</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98452166</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9564,6 +9969,11 @@
           <t>Järvsö Knärotinventering</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98452167</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9665,6 +10075,11 @@
           <t>Järvsö Knärotinventering</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98452168</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9766,6 +10181,11 @@
           <t>Järvsö Knärotinventering</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98452169</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9867,6 +10287,11 @@
           <t>Järvsö Knärotinventering</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98452170</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9968,6 +10393,11 @@
           <t>Järvsö Knärotinventering</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98452171</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10069,6 +10499,11 @@
           <t>Järvsö Knärotinventering</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98452172</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10170,6 +10605,11 @@
           <t>Järvsö Knärotinventering</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98452173</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10271,6 +10711,11 @@
           <t>Järvsö Knärotinventering</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98452174</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10372,6 +10817,11 @@
           <t>Järvsö Knärotinventering</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98452175</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10473,6 +10923,11 @@
           <t>Järvsö Knärotinventering</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98452176</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10574,6 +11029,11 @@
           <t>Järvsö Knärotinventering</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98452177</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10696,6 +11156,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102634452</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10814,6 +11279,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102634776</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10941,6 +11411,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102635248</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11063,6 +11538,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102635446</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11185,6 +11665,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102636196</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11312,6 +11797,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102636359</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11433,6 +11923,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103950345</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11557,6 +12052,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103963177</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11681,6 +12181,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103963705</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11805,6 +12310,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103964054</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11919,6 +12429,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111414049</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12033,6 +12548,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119997289</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12147,6 +12667,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119998328</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12257,6 +12782,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127896731</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12359,6 +12889,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127897152</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12469,8 +13004,122 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128358565</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>